--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-transport-du-professionnel.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-transport-du-professionnel.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3443" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3443" uniqueCount="376">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -880,6 +880,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Act.statusCode</t>
@@ -8707,7 +8711,7 @@
         <v>74</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>74</v>
+        <v>282</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>74</v>
@@ -8715,10 +8719,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8774,25 +8778,25 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8812,10 +8816,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8838,13 +8842,13 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8895,7 +8899,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8915,10 +8919,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8941,7 +8945,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8974,7 +8978,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -8992,7 +8996,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -9012,10 +9016,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9071,25 +9075,25 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9109,10 +9113,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9135,7 +9139,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9188,7 +9192,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9208,10 +9212,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9234,7 +9238,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9287,7 +9291,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9307,10 +9311,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9333,13 +9337,13 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9390,7 +9394,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9410,10 +9414,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9436,7 +9440,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9489,7 +9493,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9509,10 +9513,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9535,7 +9539,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9588,7 +9592,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9608,10 +9612,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9622,7 +9626,7 @@
         <v>75</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>141</v>
@@ -9634,13 +9638,13 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9691,7 +9695,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9711,10 +9715,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9737,13 +9741,13 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9794,7 +9798,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9814,10 +9818,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9915,10 +9919,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10016,10 +10020,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10117,10 +10121,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10218,10 +10222,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10321,10 +10325,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10424,10 +10428,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10527,10 +10531,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10630,10 +10634,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10731,10 +10735,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10771,7 +10775,7 @@
         <v>74</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>74</v>
@@ -10790,7 +10794,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>74</v>
@@ -10808,7 +10812,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>75</v>
@@ -10828,10 +10832,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10858,7 +10862,7 @@
       </c>
       <c r="L92" s="2"/>
       <c r="M92" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -10909,7 +10913,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10929,10 +10933,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10959,12 +10963,12 @@
       </c>
       <c r="L93" s="2"/>
       <c r="M93" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q93" s="2"/>
       <c r="R93" t="s" s="2">
@@ -11010,7 +11014,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -11030,10 +11034,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11109,7 +11113,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11129,10 +11133,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11155,7 +11159,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11208,7 +11212,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11228,10 +11232,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11254,7 +11258,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11307,7 +11311,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11327,10 +11331,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11353,7 +11357,7 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -11406,7 +11410,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11426,10 +11430,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11452,7 +11456,7 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -11505,7 +11509,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11525,10 +11529,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11551,7 +11555,7 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -11604,7 +11608,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11624,10 +11628,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11650,7 +11654,7 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -11703,7 +11707,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11723,10 +11727,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11749,7 +11753,7 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -11802,7 +11806,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -11822,10 +11826,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11848,7 +11852,7 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -11901,7 +11905,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -11921,10 +11925,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11947,7 +11951,7 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -12000,7 +12004,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12020,10 +12024,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12046,7 +12050,7 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -12099,7 +12103,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12119,10 +12123,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12145,7 +12149,7 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -12198,7 +12202,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12218,10 +12222,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12244,7 +12248,7 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -12297,7 +12301,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12317,10 +12321,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12343,7 +12347,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12396,7 +12400,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12416,10 +12420,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12442,7 +12446,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12495,7 +12499,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12515,10 +12519,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12541,7 +12545,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12594,7 +12598,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
